--- a/output/REM_2024_P5_SECCION_B_ADULTO_MAYOR.xlsx
+++ b/output/REM_2024_P5_SECCION_B_ADULTO_MAYOR.xlsx
@@ -160,7 +160,7 @@
     <t>Posta de Salud Rural Chacabuco (Colina)</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Dr. José Symón Ojeda</t>
+    <t>CECOSF Haydeé Sepúlveda</t>
   </si>
   <si>
     <t>Posta de Salud Rural Colorado</t>
@@ -214,7 +214,7 @@
     <t>Centro de Salud Familiar Marta Ugarte Román</t>
   </si>
   <si>
-    <t>Hospital de Til Til</t>
+    <t>Hospital Comunitario de Til Til</t>
   </si>
   <si>
     <t>Centro de Salud Familiar Cristo Vive (ONG)</t>
@@ -448,7 +448,7 @@
     <t>Centro Comunitario de Salud Familiar Padre Demetrio Bravo</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Lo Chacón</t>
+    <t>CECOSF Wilma Yoli Gomez Conejera</t>
   </si>
   <si>
     <t>Hospital de Curacaví</t>
@@ -505,7 +505,7 @@
     <t>Centro de Salud Familiar Santa Anselma</t>
   </si>
   <si>
-    <t>Centro de Salud Familiar Maipo</t>
+    <t>Centro de Salud Familiar Dragica Ciudad Pap</t>
   </si>
   <si>
     <t>Centro de Salud Familiar Confraternidad</t>
@@ -1069,7 +1069,7 @@
     <t>Servicio de Salud Metropolitano Oriente</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
   <si>
     <t>Servicio de Salud Metropolitano Central</t>
